--- a/03_Outputs/all/01_TablasDescriptivas/idx3_climatico_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx3_climatico_vr.xlsx
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>1.145199859693601</v>
+        <v>1.1451998596936</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -419,7 +419,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.8943815715104237</v>
+        <v>0.8943815715104227</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.145199859693601</v>
+        <v>1.1451998596936</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>2.105618428489577</v>
+        <v>2.105618428489576</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>3.000000000000001</v>
+        <v>2.999999999999998</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>38.17332865645336</v>
+        <v>38.17332865645335</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>32.01395229319919</v>
+        <v>32.01395229319922</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>29.81271905034745</v>
+        <v>29.81271905034744</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>38.17332865645336</v>
+        <v>38.17332865645335</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>70.18728094965255</v>
+        <v>70.18728094965256</v>
       </c>
       <c r="C12">
         <v>2</v>
